--- a/inventario desorganizado/New Intventory leo.xlsx
+++ b/inventario desorganizado/New Intventory leo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Sistema_ERP-main\Sistema_ERP-main\inventario desorganizado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15F99CB-C11E-430F-BFA3-2CDA38EFBB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF96FD5-5F62-4EE8-836C-E38B9CD31A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{28FEE727-8373-4FBC-857E-B122CC4299F2}"/>
   </bookViews>
@@ -1281,10 +1281,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="[$$-300A]#,##0;[$$-300A]\-#,##0"/>
-    <numFmt numFmtId="171" formatCode="_ [$$-300A]* #,##0.00_ ;_ [$$-300A]* \-#,##0.00_ ;_ [$$-300A]* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="172" formatCode="_-[$$-540A]* #,##0.00_ ;_-[$$-540A]* \-#,##0.00\ ;_-[$$-540A]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="175" formatCode="_-[$$-540A]* #,##0_ ;_-[$$-540A]* \-#,##0\ ;_-[$$-540A]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="164" formatCode="[$$-300A]#,##0;[$$-300A]\-#,##0"/>
+    <numFmt numFmtId="165" formatCode="_ [$$-300A]* #,##0.00_ ;_ [$$-300A]* \-#,##0.00_ ;_ [$$-300A]* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_-[$$-540A]* #,##0.00_ ;_-[$$-540A]* \-#,##0.00\ ;_-[$$-540A]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="167" formatCode="_-[$$-540A]* #,##0_ ;_-[$$-540A]* \-#,##0\ ;_-[$$-540A]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1521,7 +1521,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1555,20 +1555,18 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1896,7 +1894,7 @@
     <col min="6" max="6" width="34.21875" customWidth="1"/>
     <col min="7" max="7" width="21" customWidth="1"/>
     <col min="8" max="8" width="52.33203125" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="33" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="30" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="14" max="14" width="33" customWidth="1"/>
     <col min="18" max="18" width="34.44140625" customWidth="1"/>
@@ -2077,14 +2075,14 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I24" s="34"/>
+      <c r="I24" s="31"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="I25" s="34"/>
+      <c r="I25" s="31"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
@@ -2093,7 +2091,7 @@
       <c r="C26">
         <v>2</v>
       </c>
-      <c r="I26" s="34"/>
+      <c r="I26" s="31"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
@@ -2102,39 +2100,39 @@
       <c r="C27">
         <v>1</v>
       </c>
-      <c r="I27" s="34"/>
+      <c r="I27" s="31"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B28" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="27">
-        <v>1</v>
-      </c>
-      <c r="I28" s="34"/>
+      <c r="C28" s="34">
+        <v>1</v>
+      </c>
+      <c r="I28" s="31"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B29" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="27"/>
-      <c r="I29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="I29" s="31"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="27">
-        <v>1</v>
-      </c>
-      <c r="I30" s="34"/>
+      <c r="C30" s="34">
+        <v>1</v>
+      </c>
+      <c r="I30" s="31"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="27"/>
-      <c r="I31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="I31" s="31"/>
     </row>
     <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
@@ -2143,7 +2141,7 @@
       <c r="C32">
         <v>1</v>
       </c>
-      <c r="I32" s="34"/>
+      <c r="I32" s="31"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
@@ -2152,7 +2150,7 @@
       <c r="C33">
         <v>1</v>
       </c>
-      <c r="I33" s="34"/>
+      <c r="I33" s="31"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B34" s="7" t="s">
@@ -2161,7 +2159,7 @@
       <c r="C34">
         <v>1</v>
       </c>
-      <c r="I34" s="34"/>
+      <c r="I34" s="31"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
@@ -2170,7 +2168,7 @@
       <c r="C35">
         <v>2</v>
       </c>
-      <c r="I35" s="34"/>
+      <c r="I35" s="31"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
@@ -2179,7 +2177,7 @@
       <c r="C36">
         <v>1</v>
       </c>
-      <c r="I36" s="34"/>
+      <c r="I36" s="31"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -2194,13 +2192,13 @@
       <c r="D37">
         <v>80</v>
       </c>
-      <c r="I37" s="34"/>
+      <c r="I37" s="31"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I38" s="34"/>
+      <c r="I38" s="31"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I39" s="34"/>
+      <c r="I39" s="31"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
@@ -2351,9 +2349,6 @@
         <v>42</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B61" s="32"/>
-    </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="20" t="s">
@@ -2486,9 +2481,25 @@
         <v>2</v>
       </c>
     </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B82" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B83" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+    </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B84" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -2496,15 +2507,15 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B85" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B86" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -2512,41 +2523,25 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B87" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B88" s="2" t="s">
-        <v>52</v>
+        <v>288</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B89" s="2" t="s">
-        <v>53</v>
+      <c r="B89" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="C89">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B90" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B91" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C91">
         <v>3</v>
       </c>
     </row>
@@ -3576,7 +3571,7 @@
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B247" s="36" t="s">
+      <c r="B247" s="33" t="s">
         <v>78</v>
       </c>
       <c r="C247">
@@ -4259,7 +4254,6 @@
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A341" s="28"/>
       <c r="B341" s="2" t="s">
         <v>319</v>
       </c>
@@ -4484,18 +4478,18 @@
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B373" s="29" t="s">
+      <c r="B373" s="27" t="s">
         <v>365</v>
       </c>
       <c r="C373">
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B376" t="s">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B374" t="s">
         <v>227</v>
       </c>
-      <c r="C376">
+      <c r="C374">
         <v>1</v>
       </c>
     </row>
@@ -5532,12 +5526,9 @@
       <c r="C545">
         <v>1</v>
       </c>
-      <c r="D545" s="35">
+      <c r="D545" s="32">
         <v>86</v>
       </c>
-    </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B546" s="28"/>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B548" s="20" t="s">
@@ -5554,7 +5545,7 @@
       <c r="C549">
         <v>3</v>
       </c>
-      <c r="D549" s="30">
+      <c r="D549" s="28">
         <v>25</v>
       </c>
     </row>
@@ -5573,12 +5564,12 @@
       <c r="C553">
         <v>4</v>
       </c>
-      <c r="D553" s="31">
+      <c r="D553" s="29">
         <v>12</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D554" s="31"/>
+      <c r="D554" s="29"/>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B556" s="20" t="s">

--- a/inventario desorganizado/New Intventory leo.xlsx
+++ b/inventario desorganizado/New Intventory leo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\Sistema_ERP-main\Sistema_ERP-main\inventario desorganizado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF96FD5-5F62-4EE8-836C-E38B9CD31A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C499E94E-32CF-4C24-BF10-510684224ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{28FEE727-8373-4FBC-857E-B122CC4299F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{28FEE727-8373-4FBC-857E-B122CC4299F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -969,9 +969,6 @@
     <t>POST. WOLF 200/SPITFIRE/WOLF 250/RANGER CF2 250/HONDA CB 190</t>
   </si>
   <si>
-    <t>POST. TEKKEN</t>
-  </si>
-  <si>
     <t>POST. UNIVERSAL</t>
   </si>
   <si>
@@ -1273,6 +1270,9 @@
   </si>
   <si>
     <t>MANIGUETA EMBRAGUE SPITFIRE/DELTA/PANTHER/WORKFORCE/SKR</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>392</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>384</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
+        <v>378</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B121" s="2" t="s">
-        <v>311</v>
+        <v>412</v>
       </c>
       <c r="C121">
         <v>13</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B122" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C122">
         <v>3</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B123" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B124" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C124">
         <v>6</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="125" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B125" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C125">
         <v>3</v>
@@ -2764,7 +2764,7 @@
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B126" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C126">
         <v>5</v>
@@ -2772,7 +2772,7 @@
     </row>
     <row r="127" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B127" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C127">
         <v>3</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="128" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B128" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -2788,7 +2788,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B129" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C129">
         <v>3</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B130" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -2804,7 +2804,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B131" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C131">
         <v>2</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B132" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B133" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -2828,7 +2828,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B134" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -2836,7 +2836,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B135" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C135">
         <v>5</v>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B136" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B137" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C137">
         <v>7</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B138" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C138">
         <v>2</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B139" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C139">
         <v>5</v>
@@ -2876,7 +2876,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B140" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C140">
         <v>2</v>
@@ -2884,10 +2884,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>398</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="C141">
         <v>2</v>
@@ -2898,10 +2898,10 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>400</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="C142">
         <v>2</v>
@@ -2942,7 +2942,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B149" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C149">
         <v>2</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B150" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C150">
         <v>6</v>
@@ -3968,7 +3968,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B301" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B308" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C308">
         <v>3</v>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B313" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -4073,7 +4073,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B316" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B341" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C341">
         <v>2</v>
@@ -4263,7 +4263,7 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B342" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B343" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B344" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C344">
         <v>3</v>
@@ -4287,7 +4287,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B345" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -4295,7 +4295,7 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B346" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -4303,7 +4303,7 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B347" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C347">
         <v>2</v>
@@ -4311,7 +4311,7 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B348" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C348">
         <v>2</v>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B349" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -4327,7 +4327,7 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B350" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -4335,7 +4335,7 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B351" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B352" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -4351,7 +4351,7 @@
     </row>
     <row r="353" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B353" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -4359,7 +4359,7 @@
     </row>
     <row r="354" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B354" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -4367,7 +4367,7 @@
     </row>
     <row r="355" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B355" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C355">
         <v>2</v>
@@ -4375,7 +4375,7 @@
     </row>
     <row r="356" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B356" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="357" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B357" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -4391,7 +4391,7 @@
     </row>
     <row r="358" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B358" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C358">
         <v>1</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="359" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B359" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C359">
         <v>2</v>
@@ -4407,7 +4407,7 @@
     </row>
     <row r="360" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B360" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C360">
         <v>1</v>
@@ -4415,12 +4415,12 @@
     </row>
     <row r="363" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B363" s="20" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="364" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B364" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C364">
         <v>3</v>
@@ -4428,7 +4428,7 @@
     </row>
     <row r="365" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B365" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -4436,15 +4436,15 @@
     </row>
     <row r="366" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B366" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C366" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="367" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B367" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C367">
         <v>2</v>
@@ -4479,7 +4479,7 @@
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B373" s="27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C373">
         <v>1</v>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B379" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C379">
         <v>3</v>
@@ -4515,7 +4515,7 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B382" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C382">
         <v>11</v>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B383" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C383">
         <v>1</v>
@@ -4531,7 +4531,7 @@
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B384" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C384">
         <v>1</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
+        <v>396</v>
+      </c>
+      <c r="B389" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="B389" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="C389">
         <v>2</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B394" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C394">
         <v>4</v>
@@ -4613,7 +4613,7 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B398" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C398">
         <v>1</v>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B399" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C399">
         <v>1</v>
@@ -4629,7 +4629,7 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B400" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C400">
         <v>18</v>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B403" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C403">
         <v>1</v>
@@ -4669,7 +4669,7 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B405" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C405">
         <v>2</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="446" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B446" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C446">
         <v>1</v>
@@ -5518,10 +5518,10 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
+        <v>390</v>
+      </c>
+      <c r="B545" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="B545" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="C545">
         <v>1</v>
@@ -5532,15 +5532,15 @@
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B548" s="20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
+        <v>370</v>
+      </c>
+      <c r="B549" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="B549" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="C549">
         <v>3</v>
@@ -5551,15 +5551,15 @@
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B552" s="20" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
+        <v>372</v>
+      </c>
+      <c r="B553" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="B553" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="C553">
         <v>4</v>
@@ -5573,15 +5573,15 @@
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B556" s="20" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
+        <v>374</v>
+      </c>
+      <c r="B557" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="B557" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="C557">
         <v>4</v>
@@ -5592,15 +5592,15 @@
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B560" s="20" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
+        <v>376</v>
+      </c>
+      <c r="B561" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="B561" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="C561">
         <v>4</v>
@@ -5611,15 +5611,15 @@
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B564" s="20" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
+        <v>382</v>
+      </c>
+      <c r="B565" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="B565" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="C565">
         <v>2</v>
@@ -5630,15 +5630,15 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B568" s="20" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
+        <v>386</v>
+      </c>
+      <c r="B569" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="B569" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="C569">
         <v>3</v>
@@ -5649,15 +5649,15 @@
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B571" s="20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
+        <v>388</v>
+      </c>
+      <c r="B572" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="B572" s="2" t="s">
-        <v>390</v>
       </c>
       <c r="C572">
         <v>1</v>
@@ -5668,15 +5668,15 @@
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B575" s="20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
+        <v>394</v>
+      </c>
+      <c r="B576" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="B576" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="C576">
         <v>2</v>
